--- a/information_request_forms/022_home_value_estimate_form--information_request_forms.xlsx
+++ b/information_request_forms/022_home_value_estimate_form--information_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,8 +442,8 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What is the Address</t>
+          <t>What is the address?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,20 +571,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What is the square footage?</t>
+          <t>Square Footage</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What is the Year Built?</t>
+          <t>Year Built</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,13 +617,13 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What is the Lot Size?</t>
+          <t>Lot Size</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What is the Year Built?</t>
+          <t>Age of the Home</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,7 +653,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What is the Square Footage?</t>
+          <t>Number of Stories</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,7 +676,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What is the Number of Stories?</t>
+          <t>Is the Property a Single-Story or Multi-Story?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,20 +709,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What is the Age of the Home?</t>
+          <t>Phone Number</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -732,13 +732,13 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What is the Lot Size?</t>
+          <t>Email Address</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -755,20 +755,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What is the Square Footage?</t>
+          <t>Zip Code</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What is the Age of the Home?</t>
+          <t>Additional Notes</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,7 +791,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Additional Notes</t>
+          <t>Is this Property a Single-Family or Multi-Family Property?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Is this a Mobile Home?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,20 +847,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>What is your phone number?</t>
+          <t>Email of the Property Owner</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -870,13 +870,13 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>What is your Name?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -893,20 +893,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>What is the email?</t>
+          <t>What is your Address?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -916,13 +916,13 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>What is your email?</t>
+          <t>What is the Square Footage of the Property?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -939,20 +939,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>What is the Address?</t>
+          <t>What is the Lot Size of the Property?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -962,14 +962,10 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>What is the Age of the Home?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>prophets</t>
-        </is>
-      </c>
+          <t>Age of the Property</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>no</t>
@@ -989,20 +985,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>What is your zip code?</t>
+          <t>Zip Code of the Property</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1012,13 +1008,13 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>What is your Email?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1035,13 +1031,13 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>What is the zip code?</t>
+          <t>What is your Phone Number?</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>What is the zip?</t>
+          <t>What is the Zip of the Property?</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1071,7 +1067,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1081,13 +1077,13 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>What is the zip?</t>
+          <t>Home Value Estimate Form Page 25</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1135,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1169,947 +1165,369 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>home_value_estimate_form_page_2_choices</t>
+          <t>home_value_estimate_form_page_4_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>home_value_estimate_form_page_2_choices</t>
+          <t>home_value_estimate_form_page_4_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>home_value_estimate_form_page_2_choices</t>
+          <t>home_value_estimate_form_page_4_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>home_value_estimate_form_page_2_choices</t>
+          <t>home_value_estimate_form_page_6_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>home_value_estimate_form_page_2_choices</t>
+          <t>home_value_estimate_form_page_6_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>home_value_estimate_form_page_4_choices</t>
+          <t>home_value_estimate_form_page_6_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>home_value_estimate_form_page_4_choices</t>
+          <t>home_value_estimate_form_page_7_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>home_value_estimate_form_page_4_choices</t>
+          <t>home_value_estimate_form_page_7_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>home_value_estimate_form_page_4_choices</t>
+          <t>home_value_estimate_form_page_7_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>home_value_estimate_form_page_4_choices</t>
+          <t>home_value_estimate_form_page_8_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>home_value_estimate_form_page_4_choices</t>
+          <t>home_value_estimate_form_page_8_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>home_value_estimate_form_page_4_choices</t>
+          <t>home_value_estimate_form_page_13_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>home_value_estimate_form_page_4_choices</t>
+          <t>home_value_estimate_form_page_13_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>home_value_estimate_form_page_4_choices</t>
+          <t>home_value_estimate_form_page_14_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>home_value_estimate_form_page_4_choices</t>
+          <t>home_value_estimate_form_page_14_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>home_value_estimate_form_page_4_choices</t>
+          <t>home_value_estimate_form_page_20_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>home_value_estimate_form_page_6_choices</t>
+          <t>home_value_estimate_form_page_20_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>home_value_estimate_form_page_6_choices</t>
+          <t>home_value_estimate_form_page_20_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>home_value_estimate_form_page_6_choices</t>
+          <t>home_value_estimate_form_page_24_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>home_value_estimate_form_page_6_choices</t>
+          <t>home_value_estimate_form_page_24_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>home_value_estimate_form_page_6_choices</t>
+          <t>home_value_estimate_form_page_24_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1950</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>home_value_estimate_form_page_6_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1960</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1960</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>home_value_estimate_form_page_6_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>home_value_estimate_form_page_6_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1980</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1980</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>home_value_estimate_form_page_6_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1990</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1990</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>home_value_estimate_form_page_6_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>home_value_estimate_form_page_8_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>home_value_estimate_form_page_8_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>home_value_estimate_form_page_8_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>home_value_estimate_form_page_10_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1/4</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1/4</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>home_value_estimate_form_page_10_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>home_value_estimate_form_page_10_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>1/3</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1/3</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>home_value_estimate_form_page_10_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>1/4</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1/4</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>home_value_estimate_form_page_12_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>home_value_estimate_form_page_12_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>home_value_estimate_form_page_12_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>home_value_estimate_form_page_12_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>home_value_estimate_form_page_12_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>home_value_estimate_form_page_12_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>home_value_estimate_form_page_12_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>home_value_estimate_form_page_12_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>home_value_estimate_form_page_12_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>home_value_estimate_form_page_12_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>home_value_estimate_form_page_14_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>home_value_estimate_form_page_14_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>home_value_estimate_form_page_16_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>home_value_estimate_form_page_16_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>home_value_estimate_form_page_18_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>home_value_estimate_form_page_18_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>home_value_estimate_form_page_22_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>home_value_estimate_form_page_22_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>home_value_estimate_form_page_24_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>10001</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>10001</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>home_value_estimate_form_page_24_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>10002</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>10002</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>home_value_estimate_form_page_25_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>10001</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>10001</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>home_value_estimate_form_page_25_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>10002</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>10002</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
